--- a/app/test-data/空闲时间表.xlsx
+++ b/app/test-data/空闲时间表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luomingyu\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF31E70-076C-4516-80A6-07295AC0D0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0331E17F-253B-4B40-9EF1-F990C849C7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
